--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512472_ELIMINGRD14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512472_ELIMINGRD14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6506</v>
+        <v>6.1706</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5302</v>
+        <v>5.9334</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1204</v>
+        <v>0.2372</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8542</v>
+        <v>4.8091</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0496</v>
+        <v>2.0033</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8046</v>
+        <v>2.8058</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9647</v>
+        <v>5.1312</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4793</v>
+        <v>2.5453</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4854</v>
+        <v>2.586</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1105</v>
+        <v>-0.3221</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4297</v>
+        <v>-0.542</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3192</v>
+        <v>0.2199</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7432</v>
+        <v>-1.2169</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3533</v>
+        <v>-0.2252</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3899</v>
+        <v>-0.9917</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7396</v>
+        <v>2.7732</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8702</v>
+        <v>2.9705</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9117</v>
+        <v>2.6093</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9585</v>
+        <v>0.3612</v>
       </c>
       <c r="G3" t="n">
-        <v>4.165</v>
+        <v>4.3152</v>
       </c>
       <c r="H3" t="n">
-        <v>4.963</v>
+        <v>5.1013</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.798</v>
+        <v>-0.7861</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7974</v>
+        <v>4.1781</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1858</v>
+        <v>5.4499</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3884</v>
+        <v>-1.2718</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3676</v>
+        <v>0.1371</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2228</v>
+        <v>-0.3486</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5904</v>
+        <v>0.4857</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8344</v>
+        <v>-0.9232</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6044</v>
+        <v>-0.4015</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2299</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6273</v>
+        <v>2.0942</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6184</v>
+        <v>2.3696</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9911</v>
+        <v>-0.2754</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7682</v>
+        <v>3.0968</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0279</v>
+        <v>-0.5434</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7403</v>
+        <v>3.6402</v>
       </c>
       <c r="J4" t="n">
-        <v>6.0278</v>
+        <v>2.9715</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0643</v>
+        <v>0.2157</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9635</v>
+        <v>2.7558</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2596</v>
+        <v>0.1253</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0364</v>
+        <v>-0.7591</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2232</v>
+        <v>0.8844</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0003</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4007</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S4" t="n">
-        <v>1.599</v>
+        <v>-1.5021</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1316</v>
+        <v>-0.2972</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4674</v>
+        <v>-1.2049</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.7396</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8597</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.5993</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9599</v>
+        <v>1.6408</v>
       </c>
       <c r="E5" t="n">
-        <v>2.54</v>
+        <v>0.0868</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5800999999999999</v>
+        <v>1.554</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1813</v>
+        <v>1.098</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5355</v>
+        <v>-0.0236</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7168</v>
+        <v>1.1216</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8068</v>
+        <v>1.5505</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0872</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7196</v>
+        <v>0.7295</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3745</v>
+        <v>-0.4526</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6227</v>
+        <v>-0.8447</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9972</v>
+        <v>0.3921</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8002</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6002</v>
+        <v>-1.1684</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4004</v>
+        <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7618</v>
+        <v>0.2118</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0736</v>
+        <v>-0.2953</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.8354</v>
+        <v>0.5071</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2598</v>
+        <v>0.3311</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5196</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4483</v>
+        <v>1.2388</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1963</v>
+        <v>5.0856</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6446</v>
+        <v>-3.8468</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1474</v>
+        <v>4.844</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0138</v>
+        <v>3.121</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1336</v>
+        <v>1.723</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5197</v>
+        <v>6.3017</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7998</v>
+        <v>4.267</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7199</v>
+        <v>2.0347</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3723</v>
+        <v>-1.4577</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7859</v>
+        <v>-1.146</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4137</v>
+        <v>-0.3117</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2003</v>
+        <v>-2.3368</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0392</v>
+        <v>0.1417</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5157</v>
+        <v>0.2307</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4765</v>
+        <v>-0.0891</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3401</v>
+        <v>-2.7732</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3401</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="7">
@@ -955,31 +955,31 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1033,19 +1033,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.181</v>
+        <v>0.2967</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1934</v>
+        <v>-0.1237</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3743</v>
+        <v>0.4204</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0902</v>
+        <v>0.0309</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1934</v>
+        <v>-0.1237</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1031</v>
+        <v>0.1546</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2409</v>
+        <v>-1.3107</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9962</v>
+        <v>-1.838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7553</v>
+        <v>0.5273</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9241</v>
+        <v>-0.956</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7329</v>
+        <v>-0.7713</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1912</v>
+        <v>-0.1847</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.538</v>
+        <v>-0.5219</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06</v>
+        <v>0.0616</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3861</v>
+        <v>-0.4342</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7929</v>
+        <v>-0.8329</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0833</v>
+        <v>0.0348</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2578</v>
+        <v>-0.1477</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3411</v>
+        <v>0.1825</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5008</v>
+        <v>-1.4915</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9775</v>
+        <v>-2.538</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4767</v>
+        <v>1.0465</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2427</v>
+        <v>0.2069</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9016</v>
+        <v>-0.9571</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1442</v>
+        <v>1.1639</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3343</v>
+        <v>-0.2656</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2581</v>
+        <v>-0.2335</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0762</v>
+        <v>-0.0322</v>
       </c>
       <c r="M10" t="n">
-        <v>0.577</v>
+        <v>0.4725</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6434</v>
+        <v>-0.7236</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2204</v>
+        <v>1.1961</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3431</v>
+        <v>-0.3353</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7023</v>
+        <v>-0.4098</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3593</v>
+        <v>0.0745</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3235</v>
+        <v>-1.8246</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9156</v>
+        <v>-2.1482</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5921</v>
+        <v>0.3236</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1368</v>
+        <v>-0.2097</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.4972</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6887</v>
+        <v>-0.7068</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4906</v>
+        <v>-0.3652</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7816</v>
+        <v>0.8339</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2722</v>
+        <v>-1.1991</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3538</v>
+        <v>0.1555</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2297</v>
+        <v>-0.3367</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5835</v>
+        <v>0.4922</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0667</v>
+        <v>-1.4981</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0246</v>
+        <v>-0.4199</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0421</v>
+        <v>-1.0782</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2834</v>
+        <v>-4.0916</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7235</v>
+        <v>-2.4475</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5598</v>
+        <v>-1.6441</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9222</v>
+        <v>-0.93</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5621</v>
+        <v>-1.5785</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6399</v>
+        <v>0.6484</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0142</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9761</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0381</v>
+        <v>-0.0161</v>
       </c>
       <c r="M12" t="n">
-        <v>0.092</v>
+        <v>0.0251</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O12" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3614</v>
+        <v>-0.1352</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.509</v>
+        <v>-0.3239</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1475</v>
+        <v>0.1887</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5884</v>
+        <v>6.916899999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>5.797500000000003</v>
+        <v>8.212999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7909000000000002</v>
+        <v>-1.2961</v>
       </c>
       <c r="G13" t="n">
-        <v>17.8466</v>
+        <v>17.7638</v>
       </c>
       <c r="H13" t="n">
-        <v>7.745099999999998</v>
+        <v>7.730499999999997</v>
       </c>
       <c r="I13" t="n">
-        <v>10.1014</v>
+        <v>10.0332</v>
       </c>
       <c r="J13" t="n">
-        <v>17.939</v>
+        <v>19.2489</v>
       </c>
       <c r="K13" t="n">
-        <v>12.8236</v>
+        <v>13.6378</v>
       </c>
       <c r="L13" t="n">
-        <v>5.115399999999999</v>
+        <v>5.6112</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.09240000000000001</v>
+        <v>-1.4853</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.0783</v>
+        <v>-5.9072</v>
       </c>
       <c r="O13" t="n">
-        <v>4.986</v>
+        <v>4.4219</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.0015</v>
+        <v>-4.8685</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.0039</v>
+        <v>-13.6315</v>
       </c>
       <c r="R13" t="n">
-        <v>9.0025</v>
+        <v>8.763100000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.557700000000001</v>
+        <v>-5.191600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9553</v>
+        <v>-2.4135</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.6024</v>
+        <v>-2.7782</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6989999999999998</v>
+        <v>-0.7867999999999995</v>
       </c>
       <c r="W13" t="n">
-        <v>4.818</v>
+        <v>5.008999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.516999999999999</v>
+        <v>-5.7959</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9231</v>
+        <v>5.867</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1733</v>
+        <v>6.6008</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2502</v>
+        <v>-0.7338</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4155</v>
+        <v>-0.4213</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0469</v>
+        <v>0.0292</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4624</v>
+        <v>-0.4506</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8505</v>
+        <v>3.0719</v>
       </c>
       <c r="K14" t="n">
-        <v>2.283</v>
+        <v>2.4068</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5675</v>
+        <v>0.6651</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.266</v>
+        <v>-3.4932</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2361</v>
+        <v>-2.3776</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0299</v>
+        <v>-1.1157</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1807</v>
+        <v>0.703</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0556</v>
+        <v>0.001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8749</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1189</v>
+        <v>4.2221</v>
       </c>
       <c r="W14" t="n">
-        <v>4.3787</v>
+        <v>4.5016</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.096</v>
+        <v>2.1657</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1906</v>
+        <v>1.2577</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9054</v>
+        <v>0.9079</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4492</v>
+        <v>0.4261</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9935</v>
+        <v>0.9821</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5443</v>
+        <v>-0.556</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0215</v>
+        <v>1.0787</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5796</v>
+        <v>1.6216</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5429</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5723</v>
+        <v>-0.6526</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4261</v>
+        <v>0.578</v>
       </c>
       <c r="T15" t="n">
-        <v>0.169</v>
+        <v>0.1791</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2571</v>
+        <v>0.3989</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6801</v>
+        <v>0.496</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9115</v>
+        <v>0.018</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7685</v>
+        <v>0.4781</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6688</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0666</v>
+        <v>1.0761</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7354</v>
+        <v>-1.754</v>
       </c>
       <c r="J16" t="n">
-        <v>0.669</v>
+        <v>0.8338</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9031</v>
+        <v>2.0168</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2341</v>
+        <v>-1.183</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3377</v>
+        <v>-1.5117</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8365</v>
+        <v>-0.9407</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5013</v>
+        <v>-0.571</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0087</v>
+        <v>1.8429</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2432</v>
+        <v>1.1315</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7113</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2656</v>
+        <v>0.3673</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0445</v>
+        <v>0.1807</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2211</v>
+        <v>0.1865</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02</v>
+        <v>-0.2487</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-1.1282</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02</v>
+        <v>0.7302</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02</v>
+        <v>1.3137</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.5835</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.9789</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.4342</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0258</v>
+        <v>0.4991</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0645</v>
+        <v>0.1126</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0387</v>
+        <v>0.3865</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2598</v>
+        <v>-0.6621</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4222</v>
+        <v>0.1183</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5075</v>
+        <v>2.1311</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0853</v>
+        <v>-2.0128</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2331</v>
+        <v>0.0668</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.2403</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1267</v>
+        <v>-1.1735</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6816</v>
+        <v>3.6022</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2796</v>
+        <v>3.6666</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.598</v>
+        <v>-0.0643</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9147</v>
+        <v>-3.5354</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3861</v>
+        <v>-2.4263</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-1.1091</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8002</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8002</v>
+        <v>1.9474</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3092</v>
+        <v>0.662</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.509</v>
+        <v>0.4763</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1998</v>
+        <v>0.1857</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6802</v>
+        <v>-0.6105</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5546</v>
+        <v>-0.228</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3325</v>
+        <v>-0.0413</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8871</v>
+        <v>-0.1867</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0374</v>
+        <v>0.0205</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2266</v>
+        <v>0.0205</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1892</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3884</v>
+        <v>0.0205</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5408</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1524</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.351</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.3142</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0368</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0006</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0309</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0554</v>
+        <v>-0.0618</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0633</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5999</v>
+        <v>-0.2795</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5999</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9717</v>
+        <v>-1.2313</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9786</v>
+        <v>0.0098</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0068</v>
+        <v>-1.2411</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.454</v>
+        <v>-4.6985</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4737</v>
+        <v>-4.1544</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9803</v>
+        <v>-0.5441</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3321</v>
+        <v>-1.0723</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0161</v>
+        <v>-1.511</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.316</v>
+        <v>0.4387</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1219</v>
+        <v>-3.6262</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5424</v>
+        <v>-2.6434</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6643</v>
+        <v>-0.9828</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6002</v>
+        <v>1.7526</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6002</v>
+        <v>2.7263</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5623</v>
+        <v>0.2656</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0337</v>
+        <v>-0.0037</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5285</v>
+        <v>0.2692</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6802</v>
+        <v>1.449</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6802</v>
+        <v>2.0595</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7815</v>
+        <v>-1.7306</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3084</v>
+        <v>-2.5089</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4731</v>
+        <v>0.7783</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.8333</v>
+        <v>-2.4146</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.1941</v>
+        <v>-0.4485</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6392</v>
+        <v>-1.9661</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4317</v>
+        <v>-2.2686</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6869</v>
+        <v>-0.9801</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2552</v>
+        <v>-1.2885</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4016</v>
+        <v>-0.146</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5073</v>
+        <v>0.5316</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8943</v>
+        <v>-0.6776</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8005</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8008</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.128</v>
+        <v>0.7619</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8556</v>
+        <v>0.4218</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2724</v>
+        <v>0.3401</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3793</v>
+        <v>-0.6621</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9791</v>
+        <v>-0.6621</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4856</v>
+        <v>-5.5546</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5955</v>
+        <v>-2.9981</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8901</v>
+        <v>-2.5565</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.7692</v>
+        <v>-6.7725</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.5158</v>
+        <v>-4.5162</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2534</v>
+        <v>-2.2564</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.2826</v>
+        <v>-3.1042</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9304</v>
+        <v>-1.8241</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3522</v>
+        <v>-1.2801</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4866</v>
+        <v>-3.6683</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.5854</v>
+        <v>-2.6921</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9012</v>
+        <v>-0.9762</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1431</v>
+        <v>0.1343</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6871</v>
+        <v>0.1062</v>
       </c>
       <c r="U22" t="n">
-        <v>0.456</v>
+        <v>0.0281</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8063</v>
+        <v>-6.2129</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9642</v>
+        <v>-3.3537</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.842</v>
+        <v>-2.8592</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9793</v>
+        <v>-3.0437</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8087</v>
+        <v>-2.8393</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1706</v>
+        <v>-0.2044</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4923</v>
+        <v>-1.407</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8943</v>
+        <v>-0.8235</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.487</v>
+        <v>-1.6367</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9143</v>
+        <v>-2.0157</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4274</v>
+        <v>0.379</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0533</v>
+        <v>0.6876</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0094</v>
+        <v>0.4153</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0439</v>
+        <v>0.2722</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4799</v>
+        <v>-2.4937</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.588299999999999</v>
+        <v>-5.943099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7907999999999995</v>
+        <v>1.2961</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.797600000000001</v>
+        <v>-7.2393</v>
       </c>
       <c r="G24" t="n">
-        <v>-17.8466</v>
+        <v>-17.7638</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.7451</v>
+        <v>-7.730700000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-10.1015</v>
+        <v>-10.0333</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09230000000000049</v>
+        <v>1.485199999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>5.078399999999999</v>
+        <v>5.9073</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.986</v>
+        <v>-4.422000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-17.9388</v>
+        <v>-19.249</v>
       </c>
       <c r="N24" t="n">
-        <v>-12.8235</v>
+        <v>-13.6378</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.115400000000001</v>
+        <v>-5.6112</v>
       </c>
       <c r="P24" t="n">
-        <v>5.0014</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.002699999999999</v>
+        <v>-8.763199999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>14.0041</v>
+        <v>13.6315</v>
       </c>
       <c r="S24" t="n">
-        <v>5.557700000000001</v>
+        <v>6.1653</v>
       </c>
       <c r="T24" t="n">
-        <v>2.602300000000001</v>
+        <v>2.7783</v>
       </c>
       <c r="U24" t="n">
-        <v>2.9554</v>
+        <v>3.3869</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6990000000000003</v>
+        <v>0.7867999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>5.517</v>
+        <v>5.7959</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.818</v>
+        <v>-5.009</v>
       </c>
     </row>
   </sheetData>
